--- a/Maxplay.xlsx
+++ b/Maxplay.xlsx
@@ -201,8 +201,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="31.05" customWidth="1"/>
+    <col min="2" max="2" width="12.15" customWidth="1"/>
+    <col min="3" max="3" width="12.15" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="12.15" customWidth="1"/>
+    <col min="6" max="6" width="12.15" customWidth="1"/>
+    <col min="7" max="7" width="12.15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -215,284 +220,577 @@
     <row r="2">
       <c t="inlineStr" r="A2" s="2">
         <is>
-          <t xml:space="preserve">Grupos</t>
+          <t xml:space="preserve">Taquillas</t>
         </is>
       </c>
       <c t="inlineStr" r="B2" s="2">
         <is>
           <t xml:space="preserve">Venta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C2" s="2">
+        <is>
+          <t xml:space="preserve">Premio</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D2" s="2">
+        <is>
+          <t xml:space="preserve">Porcentaje</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E2" s="2">
+        <is>
+          <t xml:space="preserve">Utilidad</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F2" s="2">
+        <is>
+          <t xml:space="preserve">Participa</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G2" s="2">
+        <is>
+          <t xml:space="preserve">Total</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">ALEXYS LOPEZ</t>
+          <t xml:space="preserve">AG AIDE </t>
         </is>
       </c>
       <c t="inlineStr" r="B3">
         <is>
-          <t xml:space="preserve">4.810,00</t>
-        </is>
+          <t xml:space="preserve">6.935,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C3">
+        <is>
+          <t xml:space="preserve">6.000,00</t>
+        </is>
+      </c>
+      <c r="D3" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="E3" s="66">
+        <v>935.00</v>
+      </c>
+      <c r="F3" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G3" s="66">
+        <v>935.00</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">DARGENIS GONZALEZ</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B4">
-        <is>
-          <t xml:space="preserve">3.270,00</t>
-        </is>
+          <t xml:space="preserve">AG CARLIANIS </t>
+        </is>
+      </c>
+      <c r="B4" s="66">
+        <v>748.00</v>
+      </c>
+      <c r="C4" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D4" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="E4" s="66">
+        <v>748.00</v>
+      </c>
+      <c r="F4" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G4" s="66">
+        <v>748.00</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">ELKIS CARRASQUERO</t>
+          <t xml:space="preserve">AG FALCON </t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">2.267,50</t>
-        </is>
+          <t xml:space="preserve">10.085,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C5">
+        <is>
+          <t xml:space="preserve">8.400,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D5">
+        <is>
+          <t xml:space="preserve">1.613,60</t>
+        </is>
+      </c>
+      <c r="E5" s="66">
+        <v>71.40</v>
+      </c>
+      <c r="F5" s="66">
+        <v>21.42</v>
+      </c>
+      <c r="G5" s="66">
+        <v>49.98</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">FABIOLA URUMACO</t>
+          <t xml:space="preserve">AG GORDITOS CARRASQUERO </t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">22.290,00</t>
+          <t xml:space="preserve">2.040,00</t>
+        </is>
+      </c>
+      <c r="C6" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D6" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E6">
+        <is>
+          <t xml:space="preserve">2.040,00</t>
+        </is>
+      </c>
+      <c r="F6" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G6">
+        <is>
+          <t xml:space="preserve">2.040,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">GERMAN CCS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B7">
-        <is>
-          <t xml:space="preserve">27.560,00</t>
-        </is>
+          <t xml:space="preserve">AG MIS NIETOS </t>
+        </is>
+      </c>
+      <c r="B7" s="66">
+        <v>850.00</v>
+      </c>
+      <c r="C7" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D7" s="66">
+        <v>102.00</v>
+      </c>
+      <c r="E7" s="66">
+        <v>748.00</v>
+      </c>
+      <c r="F7" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G7" s="66">
+        <v>748.00</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">GMARACAIBO</t>
+          <t xml:space="preserve">AG YEIBER </t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">21.970,00</t>
+          <t xml:space="preserve">5.100,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C8">
+        <is>
+          <t xml:space="preserve">3.000,00</t>
+        </is>
+      </c>
+      <c r="D8" s="66">
+        <v>510.00</v>
+      </c>
+      <c t="inlineStr" r="E8">
+        <is>
+          <t xml:space="preserve">1.590,00</t>
+        </is>
+      </c>
+      <c r="F8" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G8">
+        <is>
+          <t xml:space="preserve">1.590,00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">GP GRANDE</t>
+          <t xml:space="preserve">ANGEL DAVID MOJAN </t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">1.930,00</t>
+          <t xml:space="preserve">11.860,00</t>
+        </is>
+      </c>
+      <c r="C9" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D9" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E9">
+        <is>
+          <t xml:space="preserve">11.860,00</t>
+        </is>
+      </c>
+      <c r="F9" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G9">
+        <is>
+          <t xml:space="preserve">11.860,00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">GRUPO GALUE</t>
+          <t xml:space="preserve">CIRUELO </t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">11.600,00</t>
+          <t xml:space="preserve">1.090,00</t>
+        </is>
+      </c>
+      <c r="C10" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D10" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E10">
+        <is>
+          <t xml:space="preserve">1.090,00</t>
+        </is>
+      </c>
+      <c r="F10" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G10">
+        <is>
+          <t xml:space="preserve">1.090,00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">GRUPO MARCO</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B11">
-        <is>
-          <t xml:space="preserve">3.630,00</t>
-        </is>
+          <t xml:space="preserve">CRUCES </t>
+        </is>
+      </c>
+      <c r="B11" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="C11" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D11" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="E11" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="F11" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G11" s="66">
+        <v>25.00</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">GRUPO PAITO</t>
+          <t xml:space="preserve">FELIX EL DORADO </t>
         </is>
       </c>
       <c r="B12" s="66">
-        <v>270.00</v>
+        <v>810.00</v>
+      </c>
+      <c r="C12" s="66">
+        <v>900.00</v>
+      </c>
+      <c r="D12" s="66">
+        <v>97.20</v>
+      </c>
+      <c r="E12" s="66">
+        <v>-187.20</v>
+      </c>
+      <c r="F12" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G12" s="66">
+        <v>-187.20</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">GRUPO SONIA</t>
+          <t xml:space="preserve">JUVENTUD </t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">11.290,00</t>
+          <t xml:space="preserve">1.700,00</t>
+        </is>
+      </c>
+      <c r="C13" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D13" s="66">
+        <v>204.00</v>
+      </c>
+      <c t="inlineStr" r="E13">
+        <is>
+          <t xml:space="preserve">1.496,00</t>
+        </is>
+      </c>
+      <c r="F13" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G13">
+        <is>
+          <t xml:space="preserve">1.496,00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">GSANRAMON</t>
+          <t xml:space="preserve">LA ESTRELLAS 2 </t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">4.720,00</t>
+          <t xml:space="preserve">5.850,00</t>
+        </is>
+      </c>
+      <c r="C14" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D14" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E14">
+        <is>
+          <t xml:space="preserve">5.850,00</t>
+        </is>
+      </c>
+      <c r="F14" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G14">
+        <is>
+          <t xml:space="preserve">5.850,00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">INVERSIONES JA</t>
-        </is>
-      </c>
-      <c r="B15" s="66">
-        <v>710.00</v>
+          <t xml:space="preserve">LA RENTABLE </t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">2.500,00</t>
+        </is>
+      </c>
+      <c r="C15" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D15" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E15">
+        <is>
+          <t xml:space="preserve">2.500,00</t>
+        </is>
+      </c>
+      <c r="F15" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G15">
+        <is>
+          <t xml:space="preserve">2.500,00</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">JOHAN SAENZ</t>
-        </is>
-      </c>
-      <c r="B16" s="66">
-        <v>700.00</v>
+          <t xml:space="preserve">MANZANILLO </t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">4.480,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">1.500,00</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E16">
+        <is>
+          <t xml:space="preserve">2.980,00</t>
+        </is>
+      </c>
+      <c r="F16" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G16">
+        <is>
+          <t xml:space="preserve">2.980,00</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">LOROGP</t>
+          <t xml:space="preserve">SAN FELIPE 1 </t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">1.200,00</t>
-        </is>
+          <t xml:space="preserve">12.590,00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">13.500,00</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="E17" s="66">
+        <v>-910.00</v>
+      </c>
+      <c r="F17" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G17" s="66">
+        <v>-910.00</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">LOTO AMERICA ONLINE</t>
-        </is>
-      </c>
-      <c r="B18" s="66">
-        <v>500.00</v>
+          <t xml:space="preserve">SAN FELIPE 2 </t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">9.750,00</t>
+        </is>
+      </c>
+      <c r="C18" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E18">
+        <is>
+          <t xml:space="preserve">9.750,00</t>
+        </is>
+      </c>
+      <c r="F18" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G18">
+        <is>
+          <t xml:space="preserve">9.750,00</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">LUIS REY</t>
+          <t xml:space="preserve">TECNOBET </t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">20.140,00</t>
+          <t xml:space="preserve">1.650,00</t>
+        </is>
+      </c>
+      <c r="C19" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D19" s="66">
+        <v>198.00</v>
+      </c>
+      <c t="inlineStr" r="E19">
+        <is>
+          <t xml:space="preserve">1.452,00</t>
+        </is>
+      </c>
+      <c r="F19" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G19">
+        <is>
+          <t xml:space="preserve">1.452,00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">MARVIN GUERRA NIUMAN</t>
+          <t xml:space="preserve">WD LUCHA </t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">70.995,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c t="inlineStr" r="A21">
-        <is>
-          <t xml:space="preserve">MS BETZONE</t>
-        </is>
-      </c>
-      <c r="B21" s="66">
-        <v>240.00</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="inlineStr" r="A22">
-        <is>
-          <t xml:space="preserve">ODUARDO</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B22">
-        <is>
-          <t xml:space="preserve">13.640,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c t="inlineStr" r="A23">
-        <is>
-          <t xml:space="preserve">ROBERTM</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B23">
-        <is>
-          <t xml:space="preserve">40.460,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c t="inlineStr" r="A24">
-        <is>
-          <t xml:space="preserve">RONALD MOLERO</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B24">
-        <is>
-          <t xml:space="preserve">2.400,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c t="inlineStr" r="A25">
-        <is>
-          <t xml:space="preserve">VICTORS</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B25">
-        <is>
-          <t xml:space="preserve">115.780,00</t>
+          <t xml:space="preserve">1.650,00</t>
+        </is>
+      </c>
+      <c r="C20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D20" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">1.650,00</t>
+        </is>
+      </c>
+      <c r="F20" s="66">
+        <v>0.00</v>
+      </c>
+      <c t="inlineStr" r="G20">
+        <is>
+          <t xml:space="preserve">1.650,00</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
 </worksheet>
 </file>